--- a/حسابداری/بانک ها/ملت/1405/14041229-14050131.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14041229-14050131.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\بانک ها\ملت\1405\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDF6E1C-BC7A-4E1F-A617-78549C9B0EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F0C48C-3540-4F8B-92FC-AAA0763CA568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A6140350-CDED-4F5D-83C6-A0AA8C2AAABE}"/>
   </bookViews>
@@ -115,7 +115,7 @@
     <t>کامزد</t>
   </si>
   <si>
-    <t>انتقال به حساب شخصی</t>
+    <t>ثبت به عنوان دارایی 1</t>
   </si>
 </sst>
 </file>
@@ -263,7 +263,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,6 +446,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -651,13 +657,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -673,6 +676,15 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1073,214 +1085,224 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>4.8171296296296295E-2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>42366</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <v>0</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>324378319</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>75000</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <v>0</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="6">
         <v>2691971942</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5" t="s">
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>4.8171296296296295E-2</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>42366</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>0</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>1524378319</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="8">
         <v>2000000000</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="4">
         <v>0</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="6">
         <v>691971942</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5" t="s">
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="7">
+        <v>133</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>0.48063657407407406</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>2402</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>0</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>1554267268</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="8">
         <v>250000450</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>0</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="6">
         <v>441971492</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5" t="s">
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="7">
+        <v>133</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>123</v>
+      </c>
+      <c r="R4" s="7">
+        <v>134</v>
+      </c>
+      <c r="S4" s="7">
+        <v>450</v>
+      </c>
+      <c r="T4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="U4" s="9" t="s">
         <v>31</v>
       </c>
     </row>

--- a/حسابداری/بانک ها/ملت/1405/14041229-14050131.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14041229-14050131.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F0C48C-3540-4F8B-92FC-AAA0763CA568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27B01F6-9F39-424F-AF5F-36C3EFAF60B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A6140350-CDED-4F5D-83C6-A0AA8C2AAABE}"/>
   </bookViews>
@@ -1174,7 +1174,7 @@
       <c r="I2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="8">
         <v>75000</v>
       </c>
       <c r="K2" s="4">
@@ -1187,9 +1187,15 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
+      <c r="Q2" s="7">
+        <v>138</v>
+      </c>
+      <c r="R2" s="7">
+        <v>186</v>
+      </c>
+      <c r="S2" s="7">
+        <v>75000</v>
+      </c>
       <c r="T2" s="4" t="s">
         <v>30</v>
       </c>

--- a/حسابداری/بانک ها/ملت/1405/14041229-14050131.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14041229-14050131.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27B01F6-9F39-424F-AF5F-36C3EFAF60B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A13D11-804B-4EA9-9240-3E70D404BB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A6140350-CDED-4F5D-83C6-A0AA8C2AAABE}"/>
   </bookViews>
   <sheets>
     <sheet name="14041229-14050131" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -657,7 +670,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -685,6 +698,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1061,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE298D1-8B4A-4D78-9B0C-50440C5930F0}">
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr defaultRowHeight="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.375" style="1" bestFit="1" customWidth="1"/>
@@ -1312,6 +1328,10 @@
         <v>31</v>
       </c>
     </row>
+    <row r="5" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J5" s="10"/>
+      <c r="L5" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
